--- a/data/dividends_info_20260609.xlsx
+++ b/data/dividends_info_20260609.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>66.41000366210938</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1355217512980654</v>
+        <v>0.1462938870778929</v>
       </c>
       <c r="J2" t="n">
         <v>279</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>58.40000152587891</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.198630105668418</v>
+        <v>1.223776207453371</v>
       </c>
       <c r="J3" t="n">
         <v>258</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.41000366210938</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1355217512980654</v>
+        <v>0.1462938870778929</v>
       </c>
       <c r="J6" t="n">
         <v>188</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.099999904632568</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.666666833181238</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>167</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.54000091552734</v>
+        <v>23.125</v>
       </c>
       <c r="I8" t="n">
-        <v>1.146983812655266</v>
+        <v>1.167567567567568</v>
       </c>
       <c r="J8" t="n">
         <v>167</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.590000152587891</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>3.577817433643719</v>
+        <v>3.603603479759853</v>
       </c>
       <c r="J9" t="n">
         <v>160</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.300000190734863</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9433961924644259</v>
+        <v>0.9293680099706825</v>
       </c>
       <c r="J12" t="n">
         <v>118</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.53499984741211</v>
+        <v>23.125</v>
       </c>
       <c r="I14" t="n">
-        <v>1.14722754089879</v>
+        <v>1.167567567567568</v>
       </c>
       <c r="J14" t="n">
         <v>104</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>66.41000366210938</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1355217512980654</v>
+        <v>0.1462938870778929</v>
       </c>
       <c r="J15" t="n">
         <v>104</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.659999847412109</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I16" t="n">
-        <v>5.300353499782643</v>
+        <v>5.263158070853988</v>
       </c>
       <c r="J16" t="n">
         <v>97</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.989999771118164</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="I19" t="n">
-        <v>4.173622863984384</v>
+        <v>4.215851724063898</v>
       </c>
       <c r="J19" t="n">
         <v>48</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.690999984741211</v>
+        <v>9.701000213623047</v>
       </c>
       <c r="I21" t="n">
-        <v>2.682901665559574</v>
+        <v>2.680136009428016</v>
       </c>
       <c r="J21" t="n">
         <v>41</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.72000026702881</v>
+        <v>14.61999988555908</v>
       </c>
       <c r="I22" t="n">
-        <v>4.076086882579305</v>
+        <v>4.103967200387262</v>
       </c>
       <c r="J22" t="n">
         <v>41</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.680000066757202</v>
+        <v>3.670000076293945</v>
       </c>
       <c r="I23" t="n">
-        <v>5.978260761116315</v>
+        <v>5.994550284101392</v>
       </c>
       <c r="J23" t="n">
         <v>41</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.114999771118164</v>
+        <v>6.110000133514404</v>
       </c>
       <c r="I25" t="n">
-        <v>1.635323037497259</v>
+        <v>1.636661175365329</v>
       </c>
       <c r="J25" t="n">
         <v>41</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>34</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.300000190734863</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5376343975757395</v>
+        <v>0.5494505264177207</v>
       </c>
       <c r="J28" t="n">
         <v>34</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.740000009536743</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I29" t="n">
-        <v>5.474452535690348</v>
+        <v>5.514705824346692</v>
       </c>
       <c r="J29" t="n">
         <v>34</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.53000020980835</v>
+        <v>4.449999809265137</v>
       </c>
       <c r="I31" t="n">
-        <v>1.545253791565751</v>
+        <v>1.573033775288176</v>
       </c>
       <c r="J31" t="n">
         <v>27</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.84999847412109</v>
+        <v>34</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4431314823091574</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="J32" t="n">
         <v>27</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.75</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6779660907362907</v>
       </c>
       <c r="J33" t="n">
         <v>20</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>23.31999969482422</v>
+        <v>23.05999946594238</v>
       </c>
       <c r="I34" t="n">
-        <v>4.073756485557968</v>
+        <v>4.11968786644192</v>
       </c>
       <c r="J34" t="n">
         <v>13</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.29999923706055</v>
+        <v>29.75</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6435643726402855</v>
+        <v>0.6554621848739496</v>
       </c>
       <c r="J35" t="n">
         <v>13</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.830000042915344</v>
+        <v>1.774999976158142</v>
       </c>
       <c r="I36" t="n">
-        <v>1.803278646235889</v>
+        <v>1.859154954549695</v>
       </c>
       <c r="J36" t="n">
         <v>13</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.255000114440918</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I37" t="n">
-        <v>5.518553638144938</v>
+        <v>5.576923281483404</v>
       </c>
       <c r="J37" t="n">
         <v>13</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.789999961853027</v>
+        <v>3.759999990463257</v>
       </c>
       <c r="I38" t="n">
-        <v>4.221635926396472</v>
+        <v>4.255319159729225</v>
       </c>
       <c r="J38" t="n">
         <v>13</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.684000015258789</v>
+        <v>2.697999954223633</v>
       </c>
       <c r="I39" t="n">
-        <v>5.163934396872063</v>
+        <v>5.137138708361582</v>
       </c>
       <c r="J39" t="n">
         <v>13</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>53.2400016784668</v>
+        <v>52.02999877929688</v>
       </c>
       <c r="I40" t="n">
-        <v>1.183320774114113</v>
+        <v>1.21083992846581</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.099999904632568</v>
+        <v>6.085000038146973</v>
       </c>
       <c r="I41" t="n">
-        <v>2.295082003094439</v>
+        <v>2.300739508994865</v>
       </c>
       <c r="J41" t="n">
         <v>13</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.39999961853027</v>
+        <v>17.75</v>
       </c>
       <c r="I42" t="n">
-        <v>4.239130522668477</v>
+        <v>4.394366197183099</v>
       </c>
       <c r="J42" t="n">
         <v>13</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27.11000061035156</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="I43" t="n">
-        <v>3.135374330000715</v>
+        <v>3.187101603181231</v>
       </c>
       <c r="J43" t="n">
         <v>13</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>66.41000366210938</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1355217512980654</v>
+        <v>0.1462938870778929</v>
       </c>
       <c r="J44" t="n">
         <v>13</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.350000023841858</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7407407276587887</v>
+        <v>0.7352941099128922</v>
       </c>
       <c r="J45" t="n">
         <v>13</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.308000087738037</v>
+        <v>6.328000068664551</v>
       </c>
       <c r="I46" t="n">
-        <v>2.874128051336342</v>
+        <v>2.865044216699277</v>
       </c>
       <c r="J46" t="n">
         <v>13</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.14999961853027</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="I48" t="n">
-        <v>2.729064141975897</v>
+        <v>2.739861616286532</v>
       </c>
       <c r="J48" t="n">
         <v>13</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.073999881744385</v>
+        <v>3.052000045776367</v>
       </c>
       <c r="I50" t="n">
-        <v>3.578399617165208</v>
+        <v>3.604193917107829</v>
       </c>
       <c r="J50" t="n">
         <v>6</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.980000019073486</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="I51" t="n">
-        <v>1.212121200444759</v>
+        <v>1.256544524576805</v>
       </c>
       <c r="J51" t="n">
         <v>6</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.005000114440918</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I52" t="n">
-        <v>5.324459031834949</v>
+        <v>5.280528102665716</v>
       </c>
       <c r="J52" t="n">
         <v>-1</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="I53" t="n">
-        <v>2.808988809194278</v>
+        <v>2.87356320264113</v>
       </c>
       <c r="J53" t="n">
         <v>-1</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.20000076293945</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="I54" t="n">
-        <v>4.080882238475512</v>
+        <v>4.095940901753599</v>
       </c>
       <c r="J54" t="n">
         <v>-5</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8939999938011169</v>
+        <v>0.8759999871253967</v>
       </c>
       <c r="I55" t="n">
-        <v>3.35570472125461</v>
+        <v>3.42465758457889</v>
       </c>
       <c r="J55" t="n">
         <v>-8</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4824999868869781</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I56" t="n">
-        <v>4.766839507787918</v>
+        <v>4.771784298454558</v>
       </c>
       <c r="J56" t="n">
         <v>-8</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.399999618530273</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="I58" t="n">
-        <v>2.127659660812527</v>
+        <v>2.109704743222172</v>
       </c>
       <c r="J58" t="n">
         <v>-8</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.450000047683716</v>
+        <v>2.454999923706055</v>
       </c>
       <c r="I59" t="n">
-        <v>7.346938632518639</v>
+        <v>7.331975787937011</v>
       </c>
       <c r="J59" t="n">
         <v>-15</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.61000061035156</v>
+        <v>16.72999954223633</v>
       </c>
       <c r="I61" t="n">
-        <v>1.505117343850047</v>
+        <v>1.494321618890983</v>
       </c>
       <c r="J61" t="n">
         <v>-15</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.990000009536743</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7518796974510066</v>
+        <v>0.753768840608794</v>
       </c>
       <c r="J62" t="n">
         <v>-15</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.119999885559082</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I63" t="n">
-        <v>3.640776800158699</v>
+        <v>3.62318852264441</v>
       </c>
       <c r="J63" t="n">
         <v>-15</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.64999961853027</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="I64" t="n">
-        <v>4.584980375417487</v>
+        <v>4.621513873985353</v>
       </c>
       <c r="J64" t="n">
         <v>-15</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.64000034332275</v>
+        <v>10.5</v>
       </c>
       <c r="I66" t="n">
-        <v>2.725563821828188</v>
+        <v>2.761904761904761</v>
       </c>
       <c r="J66" t="n">
         <v>-22</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.099999904632568</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I67" t="n">
-        <v>3.666666833181238</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J67" t="n">
         <v>-22</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>40.63000106811523</v>
+        <v>40.75</v>
       </c>
       <c r="I68" t="n">
-        <v>4.036426179882641</v>
+        <v>4.024539877300613</v>
       </c>
       <c r="J68" t="n">
         <v>-22</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>35.93999862670898</v>
+        <v>35.22000122070312</v>
       </c>
       <c r="I69" t="n">
-        <v>5.564830485312513</v>
+        <v>5.678591512439682</v>
       </c>
       <c r="J69" t="n">
         <v>-22</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.180000066757202</v>
+        <v>3.114000082015991</v>
       </c>
       <c r="I70" t="n">
-        <v>3.144654022035124</v>
+        <v>3.211303704759712</v>
       </c>
       <c r="J70" t="n">
         <v>-22</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3906842105263158</v>
+        <v>0.4012432432432432</v>
       </c>
       <c r="J71" t="n">
         <v>-22</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>21.04000091552734</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="I72" t="n">
-        <v>4.372623383875653</v>
+        <v>4.414587299730683</v>
       </c>
       <c r="J72" t="n">
         <v>-22</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.27999973297119</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="I73" t="n">
-        <v>2.659574531044594</v>
+        <v>2.712477293110238</v>
       </c>
       <c r="J73" t="n">
         <v>-22</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>86.68000030517578</v>
+        <v>87.12000274658203</v>
       </c>
       <c r="I74" t="n">
-        <v>1.199815408789172</v>
+        <v>1.193755701575437</v>
       </c>
       <c r="J74" t="n">
         <v>-22</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>44.13000106811523</v>
+        <v>43.70000076293945</v>
       </c>
       <c r="I75" t="n">
-        <v>1.586222485967179</v>
+        <v>1.60183063564989</v>
       </c>
       <c r="J75" t="n">
         <v>-22</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>58.40000152587891</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="I76" t="n">
-        <v>3.767123189243599</v>
+        <v>3.846153794853453</v>
       </c>
       <c r="J76" t="n">
         <v>-22</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.39999961853027</v>
+        <v>10.36999988555908</v>
       </c>
       <c r="I77" t="n">
-        <v>8.269231072544358</v>
+        <v>8.293153418425852</v>
       </c>
       <c r="J77" t="n">
         <v>-22</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>12.82800006866455</v>
+        <v>12.62600040435791</v>
       </c>
       <c r="I78" t="n">
-        <v>4.365450553496126</v>
+        <v>4.435292112035051</v>
       </c>
       <c r="J78" t="n">
         <v>-22</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.279999971389771</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="I79" t="n">
-        <v>1.754385986926923</v>
+        <v>1.731601774494826</v>
       </c>
       <c r="J79" t="n">
         <v>-22</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>9.210000038146973</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I80" t="n">
-        <v>3.257328976736456</v>
+        <v>3.409090835200855</v>
       </c>
       <c r="J80" t="n">
         <v>-22</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.190000057220459</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I81" t="n">
-        <v>4.931506720464348</v>
+        <v>4.954128288658833</v>
       </c>
       <c r="J81" t="n">
         <v>-22</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>91.69999694824219</v>
+        <v>90.80000305175781</v>
       </c>
       <c r="I82" t="n">
-        <v>2.246455909003701</v>
+        <v>2.268722390709347</v>
       </c>
       <c r="J82" t="n">
         <v>-22</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.90999984741211</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="I83" t="n">
-        <v>4.714016387133992</v>
+        <v>4.866969548516588</v>
       </c>
       <c r="J83" t="n">
         <v>-22</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.46000003814697</v>
+        <v>14.3100004196167</v>
       </c>
       <c r="I84" t="n">
-        <v>2.074688791207255</v>
+        <v>2.096435997225747</v>
       </c>
       <c r="J84" t="n">
         <v>-22</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>50.40000152587891</v>
+        <v>49.59999847412109</v>
       </c>
       <c r="I85" t="n">
-        <v>1.686507885448278</v>
+        <v>1.713709730139386</v>
       </c>
       <c r="J85" t="n">
         <v>-22</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>35.97999954223633</v>
+        <v>35.54000091552734</v>
       </c>
       <c r="I86" t="n">
-        <v>2.362423598705717</v>
+        <v>2.391671294607753</v>
       </c>
       <c r="J86" t="n">
         <v>-22</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>70.62000274658203</v>
+        <v>70.72000122070312</v>
       </c>
       <c r="I87" t="n">
-        <v>1.840838217841785</v>
+        <v>1.838235262387733</v>
       </c>
       <c r="J87" t="n">
         <v>-22</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.900000095367432</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="I88" t="n">
-        <v>8.695652053727246</v>
+        <v>8.771929628875695</v>
       </c>
       <c r="J88" t="n">
         <v>-22</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.5</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I89" t="n">
-        <v>7.230769230769231</v>
+        <v>7.286821920907129</v>
       </c>
       <c r="J89" t="n">
         <v>-22</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.590000152587891</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I90" t="n">
-        <v>3.577817433643719</v>
+        <v>3.603603479759853</v>
       </c>
       <c r="J90" t="n">
         <v>-22</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>24.65999984741211</v>
+        <v>24.18000030517578</v>
       </c>
       <c r="I91" t="n">
-        <v>4.055150065643423</v>
+        <v>4.135649244743591</v>
       </c>
       <c r="J91" t="n">
         <v>-22</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.75</v>
+        <v>4.710000038146973</v>
       </c>
       <c r="I92" t="n">
-        <v>4.526315789473684</v>
+        <v>4.56475580167057</v>
       </c>
       <c r="J92" t="n">
         <v>-22</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.53499984741211</v>
+        <v>23.125</v>
       </c>
       <c r="I93" t="n">
-        <v>1.14722754089879</v>
+        <v>1.167567567567568</v>
       </c>
       <c r="J93" t="n">
         <v>-22</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.859999656677246</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="I94" t="n">
-        <v>2.028397636551223</v>
+        <v>2.004008107952115</v>
       </c>
       <c r="J94" t="n">
         <v>-22</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.689999580383301</v>
+        <v>8.569999694824219</v>
       </c>
       <c r="I95" t="n">
-        <v>2.761795300218116</v>
+        <v>2.800466844181407</v>
       </c>
       <c r="J95" t="n">
         <v>-22</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>21.8700008392334</v>
+        <v>21.44000053405762</v>
       </c>
       <c r="I96" t="n">
-        <v>3.61225409092253</v>
+        <v>3.684701400753598</v>
       </c>
       <c r="J96" t="n">
         <v>-22</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.480000019073486</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I97" t="n">
-        <v>1.697080286064008</v>
+        <v>1.722222191806684</v>
       </c>
       <c r="J97" t="n">
         <v>-22</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.15999984741211</v>
+        <v>33.86000061035156</v>
       </c>
       <c r="I99" t="n">
-        <v>1.024590168511126</v>
+        <v>1.033668026258095</v>
       </c>
       <c r="J99" t="n">
         <v>-22</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.715000152587891</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="I100" t="n">
-        <v>8.254653572664159</v>
+        <v>8.347891734121053</v>
       </c>
       <c r="J100" t="n">
         <v>-22</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.240000009536743</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I101" t="n">
-        <v>2.678571417167479</v>
+        <v>2.690582936628342</v>
       </c>
       <c r="J101" t="n">
         <v>-22</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>14</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="I102" t="n">
-        <v>1.428571428571429</v>
+        <v>1.413427599942038</v>
       </c>
       <c r="J102" t="n">
         <v>-22</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.159999847412109</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="I103" t="n">
-        <v>1.438547516690633</v>
+        <v>1.463068189745969</v>
       </c>
       <c r="J103" t="n">
         <v>-22</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.747000217437744</v>
+        <v>5.645999908447266</v>
       </c>
       <c r="I104" t="n">
-        <v>3.306072608514882</v>
+        <v>3.365214365585295</v>
       </c>
       <c r="J104" t="n">
         <v>-22</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.52499961853027</v>
+        <v>10.51500034332275</v>
       </c>
       <c r="I105" t="n">
-        <v>4.104513212897628</v>
+        <v>4.10841641364595</v>
       </c>
       <c r="J105" t="n">
         <v>-22</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.43000030517578</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I106" t="n">
-        <v>1.664774857811238</v>
+        <v>1.666666690749352</v>
       </c>
       <c r="J106" t="n">
         <v>-22</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.949999809265137</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I108" t="n">
-        <v>6.762590113649165</v>
+        <v>6.911764512012579</v>
       </c>
       <c r="J108" t="n">
         <v>-22</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>55.63999938964844</v>
+        <v>55.86000061035156</v>
       </c>
       <c r="I109" t="n">
-        <v>2.51617544097325</v>
+        <v>2.506265636775812</v>
       </c>
       <c r="J109" t="n">
         <v>-22</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.377000093460083</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="I110" t="n">
-        <v>8.88362427294514</v>
+        <v>8.98203615896238</v>
       </c>
       <c r="J110" t="n">
         <v>-22</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="I111" t="n">
-        <v>0.75</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J111" t="n">
         <v>-22</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.410000085830688</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="I112" t="n">
-        <v>4.98533711791938</v>
+        <v>5.014749107354538</v>
       </c>
       <c r="J112" t="n">
         <v>-22</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="I113" t="n">
-        <v>3.181818181818182</v>
+        <v>3.218390804597701</v>
       </c>
       <c r="J113" t="n">
         <v>-22</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.599999904632568</v>
+        <v>2.640000104904175</v>
       </c>
       <c r="I114" t="n">
-        <v>1.346153895530477</v>
+        <v>1.325757523076705</v>
       </c>
       <c r="J114" t="n">
         <v>-22</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.570000171661377</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I115" t="n">
-        <v>5.924595867679662</v>
+        <v>5.956678741377123</v>
       </c>
       <c r="J115" t="n">
         <v>-22</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9470000267028809</v>
+        <v>0.9399999976158142</v>
       </c>
       <c r="I116" t="n">
-        <v>7.391763255141106</v>
+        <v>7.446808529526145</v>
       </c>
       <c r="J116" t="n">
         <v>-22</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.90000152587891</v>
+        <v>50.95000076293945</v>
       </c>
       <c r="I117" t="n">
-        <v>1.394891903174143</v>
+        <v>1.393523040958318</v>
       </c>
       <c r="J117" t="n">
         <v>-22</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>104.1999969482422</v>
+        <v>102.3000030517578</v>
       </c>
       <c r="I118" t="n">
-        <v>1.295585450612409</v>
+        <v>1.319648054474621</v>
       </c>
       <c r="J118" t="n">
         <v>-22</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.320000171661377</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I119" t="n">
-        <v>1.092896149233872</v>
+        <v>1.095890382325411</v>
       </c>
       <c r="J119" t="n">
         <v>-22</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.462999820709229</v>
+        <v>4.40500020980835</v>
       </c>
       <c r="I121" t="n">
-        <v>3.809097172963472</v>
+        <v>3.859250667490803</v>
       </c>
       <c r="J121" t="n">
         <v>-22</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>60.20000076293945</v>
+        <v>60</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7475082961743593</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>-22</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.840000152587891</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6849314889533817</v>
+        <v>0.7117437867353402</v>
       </c>
       <c r="J124" t="n">
         <v>-22</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.11999893188477</v>
+        <v>37.86000061035156</v>
       </c>
       <c r="I125" t="n">
-        <v>2.754459678438624</v>
+        <v>2.773375549584414</v>
       </c>
       <c r="J125" t="n">
         <v>-22</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>16.48999977111816</v>
+        <v>16.36000061035156</v>
       </c>
       <c r="I127" t="n">
-        <v>2.304426957394874</v>
+        <v>2.322738299652387</v>
       </c>
       <c r="J127" t="n">
         <v>-22</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>27.21999931335449</v>
+        <v>26.32999992370605</v>
       </c>
       <c r="I128" t="n">
-        <v>2.204261627977456</v>
+        <v>2.27876947109215</v>
       </c>
       <c r="J128" t="n">
         <v>-22</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.75</v>
+        <v>37.84999847412109</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9271523178807947</v>
+        <v>0.924702811386645</v>
       </c>
       <c r="J129" t="n">
         <v>-22</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3.220000028610229</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="I130" t="n">
-        <v>0.527950305868081</v>
+        <v>0.5379746689320455</v>
       </c>
       <c r="J130" t="n">
         <v>-22</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.910000085830688</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3436426015480821</v>
+        <v>0.3558718933676701</v>
       </c>
       <c r="J131" t="n">
         <v>-22</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>23.03000068664551</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="I132" t="n">
-        <v>4.863221739500245</v>
+        <v>4.903677725558589</v>
       </c>
       <c r="J132" t="n">
         <v>-22</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.319999694824219</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I134" t="n">
-        <v>2.789699662161886</v>
+        <v>2.807775308569248</v>
       </c>
       <c r="J134" t="n">
         <v>-22</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.206000089645386</v>
+        <v>2.20799994468689</v>
       </c>
       <c r="I135" t="n">
-        <v>4.184043347651777</v>
+        <v>4.180253727908893</v>
       </c>
       <c r="J135" t="n">
         <v>-22</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.239999771118164</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I136" t="n">
-        <v>3.787878881707432</v>
+        <v>3.820960762339775</v>
       </c>
       <c r="J136" t="n">
         <v>-29</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>6.5</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I137" t="n">
-        <v>1.476923076923077</v>
+        <v>1.573770516407615</v>
       </c>
       <c r="J137" t="n">
         <v>-29</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.199999809265137</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I138" t="n">
-        <v>4.838709826275912</v>
+        <v>4.918032863773797</v>
       </c>
       <c r="J138" t="n">
         <v>-29</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>11.5</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="I139" t="n">
-        <v>1.739130434782609</v>
+        <v>1.785714316124819</v>
       </c>
       <c r="J139" t="n">
         <v>-29</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2.240000009536743</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I142" t="n">
-        <v>2.678571417167479</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J142" t="n">
         <v>-29</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.5</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="I143" t="n">
-        <v>3.225806451612903</v>
+        <v>3.289473725487982</v>
       </c>
       <c r="J143" t="n">
         <v>-29</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.700000047683716</v>
+        <v>3.920000076293945</v>
       </c>
       <c r="I144" t="n">
-        <v>2.702702667871647</v>
+        <v>2.551020358513417</v>
       </c>
       <c r="J144" t="n">
         <v>-29</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.150000095367432</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="I145" t="n">
-        <v>3.492063386339963</v>
+        <v>3.459119424238636</v>
       </c>
       <c r="J145" t="n">
         <v>-29</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>8.550000190734863</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I146" t="n">
-        <v>0.9941520246059123</v>
+        <v>1.049382666628677</v>
       </c>
       <c r="J146" t="n">
         <v>-29</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.769999980926514</v>
+        <v>4.789999961853027</v>
       </c>
       <c r="I147" t="n">
-        <v>1.991614263728936</v>
+        <v>1.983298554416876</v>
       </c>
       <c r="J147" t="n">
         <v>-29</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1.309999942779541</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="I148" t="n">
-        <v>2.290076435907805</v>
+        <v>2.343750052386896</v>
       </c>
       <c r="J148" t="n">
         <v>-29</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.399999618530273</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I149" t="n">
-        <v>1.071428620085427</v>
+        <v>1.04651158148692</v>
       </c>
       <c r="J149" t="n">
         <v>-29</v>
@@ -9497,163 +9497,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CLABO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Otofarma S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>